--- a/input/nombres_sociales.xlsx
+++ b/input/nombres_sociales.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:G198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -382,7 +382,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>url_colab</t>
+          <t>url_colab.x</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>url_colab.y</t>
         </is>
       </c>
     </row>
@@ -471,6 +476,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-104</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-104</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -503,6 +513,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-99</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-99</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -535,6 +550,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-78</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-78</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -616,6 +636,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-68</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-68</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -648,6 +673,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-31</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-31</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -734,6 +764,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-15</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-15</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +828,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-114</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-114</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -933,6 +973,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-24</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-24</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -965,6 +1010,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-4</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-4</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1024,6 +1074,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-116</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-116</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1056,6 +1111,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-17</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-17</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1088,6 +1148,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-65</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-65</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1120,6 +1185,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-3</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-3</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1152,6 +1222,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-52</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-52</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1184,6 +1259,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-55</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-55</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1297,6 +1377,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-29</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-29</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1329,6 +1414,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-23</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-23</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1496,6 +1586,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-20</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-20</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1528,6 +1623,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-80</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-80</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1614,6 +1714,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-5</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-5</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1646,6 +1751,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-71</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-71</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1862,6 +1972,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-33</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-33</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2110,6 +2225,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-101</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-101</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2169,6 +2289,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-111</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-111</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2255,6 +2380,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-46</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-46</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2314,6 +2444,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-38</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-38</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2346,6 +2481,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-35</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-35</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2459,6 +2599,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-36</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-36</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2572,6 +2717,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-70</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-70</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2604,6 +2754,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-51</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-51</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2744,6 +2899,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-86</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-86</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2830,6 +2990,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-113</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-113</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2862,6 +3027,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-112</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-112</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2948,6 +3118,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-108</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-108</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3007,6 +3182,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-89</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-89</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3039,6 +3219,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-27</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-27</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3152,6 +3337,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-6</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-6</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3319,6 +3509,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-115</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-115</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3351,6 +3546,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-30</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-30</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3378,6 +3578,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-72</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-72</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3410,6 +3615,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-14</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-14</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3442,6 +3652,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-13</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-13</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3474,6 +3689,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-7</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-7</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3533,6 +3753,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-96</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-96</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3565,6 +3790,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-54</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-54</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3597,6 +3827,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-66</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-66</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3683,6 +3918,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-63</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-63</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3850,6 +4090,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-39</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-39</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3882,6 +4127,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-28</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-28</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3941,6 +4191,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-44</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-44</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4000,6 +4255,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-56</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-56</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4086,6 +4346,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-90</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-90</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4110,7 +4375,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>María Gabriela Rubilar</t>
+          <t>Gabriela Rubilar</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-9</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-9</t>
         </is>
       </c>
     </row>
@@ -4199,6 +4474,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-32</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-32</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4231,6 +4511,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-16</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-16</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4263,6 +4548,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-1</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-1</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4403,6 +4693,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-21</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-21</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4435,6 +4730,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-60</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-60</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4575,6 +4875,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-8</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-8</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4607,6 +4912,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-12</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-12</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4666,6 +4976,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-25</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-25</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4698,6 +5013,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-45</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-45</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4757,6 +5077,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-50</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-50</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4870,6 +5195,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-79</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-79</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4902,6 +5232,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-18</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-18</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5069,6 +5404,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-22</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-22</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5290,6 +5630,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-11</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-11</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5322,6 +5667,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-109</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-109</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5354,6 +5704,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-34</t>
         </is>
       </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-34</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5602,6 +5957,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-97</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-97</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5661,6 +6021,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-59</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-59</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5828,6 +6193,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-2</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-2</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5860,6 +6230,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-40</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-40</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5892,6 +6267,11 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-69</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-69</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5920,6 +6300,11 @@
         </is>
       </c>
       <c r="F193" t="inlineStr">
+        <is>
+          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-87</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
         <is>
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-87</t>
         </is>

--- a/input/nombres_sociales.xlsx
+++ b/input/nombres_sociales.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G198"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -382,12 +382,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>url_colab.x</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>url_colab.y</t>
+          <t>url_colab</t>
         </is>
       </c>
     </row>
@@ -476,11 +471,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-104</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-104</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -513,11 +503,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-99</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-99</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -550,11 +535,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-78</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-78</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -636,11 +616,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-68</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-68</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -673,11 +648,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-31</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-31</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -764,11 +734,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-15</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-15</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -828,11 +793,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-114</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-114</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -973,11 +933,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-24</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-24</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1010,11 +965,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-4</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-4</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1074,11 +1024,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-116</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-116</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1111,11 +1056,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-17</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-17</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1148,11 +1088,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-65</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-65</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1185,11 +1120,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-3</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-3</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1222,11 +1152,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-52</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-52</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1259,11 +1184,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-55</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-55</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1377,11 +1297,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-29</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-29</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1414,11 +1329,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-23</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-23</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1586,11 +1496,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-20</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-20</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1623,11 +1528,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-80</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-80</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1714,11 +1614,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-5</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-5</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1751,11 +1646,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-71</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-71</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1972,11 +1862,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-33</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-33</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2225,11 +2110,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-101</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-101</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2289,11 +2169,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-111</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-111</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2380,11 +2255,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-46</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-46</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2444,11 +2314,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-38</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-38</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2481,11 +2346,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-35</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-35</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2599,11 +2459,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-36</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-36</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2717,11 +2572,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-70</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-70</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2754,11 +2604,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-51</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-51</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2899,11 +2744,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-86</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-86</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2990,11 +2830,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-113</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-113</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3027,11 +2862,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-112</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-112</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3118,11 +2948,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-108</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-108</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3182,11 +3007,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-89</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-89</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3219,11 +3039,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-27</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-27</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3337,11 +3152,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-6</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-6</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3509,11 +3319,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-115</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-115</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3546,11 +3351,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-30</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-30</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3578,11 +3378,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-72</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-72</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3615,11 +3410,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-14</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-14</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3652,11 +3442,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-13</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-13</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3689,11 +3474,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-7</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-7</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3753,11 +3533,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-96</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-96</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3790,11 +3565,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-54</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-54</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3827,11 +3597,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-66</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-66</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3918,11 +3683,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-63</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-63</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4090,11 +3850,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-39</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-39</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4127,11 +3882,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-28</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-28</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4191,11 +3941,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-44</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-44</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4255,11 +4000,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-56</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-56</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4346,11 +4086,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-90</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-90</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4383,11 +4118,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-9</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-9</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4474,11 +4204,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-32</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-32</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4511,11 +4236,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-16</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-16</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4548,11 +4268,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-1</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-1</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4693,11 +4408,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-21</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-21</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4730,11 +4440,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-60</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-60</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4875,11 +4580,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-8</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-8</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4912,11 +4612,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-12</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-12</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4976,11 +4671,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-25</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-25</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5013,11 +4703,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-45</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-45</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5077,11 +4762,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-50</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-50</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5195,11 +4875,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-79</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-79</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5232,11 +4907,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-18</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-18</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5404,11 +5074,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-22</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-22</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5630,11 +5295,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-11</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-11</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5667,11 +5327,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-109</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-109</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5704,11 +5359,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-34</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-34</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5957,11 +5607,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-97</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-97</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6021,11 +5666,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-59</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-59</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6193,11 +5833,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-2</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-2</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6230,11 +5865,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-40</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-40</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6267,11 +5897,6 @@
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-69</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-69</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6300,11 +5925,6 @@
         </is>
       </c>
       <c r="F193" t="inlineStr">
-        <is>
-          <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-87</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
         <is>
           <t>https://colaboratoriocienciassociales.uchile.cl/investigadores-ficha-87</t>
         </is>
